--- a/JetfWeb/JETFTAX/Download/批量上傳處理方式_範例.xlsx
+++ b/JetfWeb/JETFTAX/Download/批量上傳處理方式_範例.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\TFS\Thus\JETFTAX\JETFTAX\Download\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Source\Jetf\JetfWeb\JETFTAX\Download\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B21585A-A4F7-4016-8E54-B90FF959B202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD792C77-AD34-4196-84BA-42085EE06E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="3444" windowWidth="30156" windowHeight="14436" xr2:uid="{383CEC6D-FC70-4630-A6C8-CB46EF0EC708}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{383CEC6D-FC70-4630-A6C8-CB46EF0EC708}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>2511208SJ8DUGS</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -47,6 +47,14 @@
   </si>
   <si>
     <t>原單轉出</t>
+  </si>
+  <si>
+    <t>退件原因</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拒收</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -437,7 +445,7 @@
     <col min="1" max="1" width="18.21875" customWidth="1"/>
     <col min="2" max="2" width="19.109375" customWidth="1"/>
     <col min="3" max="3" width="15.21875" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="17.44140625" customWidth="1"/>
     <col min="5" max="5" width="18.109375" customWidth="1"/>
     <col min="6" max="6" width="18.88671875" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
@@ -451,9 +459,11 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -466,6 +476,9 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
         <v>4</v>
       </c>
     </row>
